--- a/PV_sem_outliers.xlsx
+++ b/PV_sem_outliers.xlsx
@@ -431,28 +431,34 @@
         </is>
       </c>
       <c r="C2">
-        <v>23.036</v>
+        <v>31.349</v>
       </c>
       <c r="D2">
-        <v>26.915</v>
+        <v>35.90283333333333</v>
       </c>
       <c r="E2">
-        <v>28.654</v>
+        <v>22.66416666666667</v>
       </c>
       <c r="F2">
-        <v>23.1025</v>
-      </c>
-      <c r="G2">
-        <v>40.356</v>
+        <v>21.92875</v>
       </c>
       <c r="H2">
-        <v>21.111</v>
+        <v>28.5514</v>
+      </c>
+      <c r="I2">
+        <v>26.108</v>
       </c>
       <c r="J2">
-        <v>44.3835</v>
+        <v>24.285</v>
+      </c>
+      <c r="K2">
+        <v>24.0794</v>
       </c>
       <c r="L2">
-        <v>50.302</v>
+        <v>31.44025</v>
+      </c>
+      <c r="M2">
+        <v>26.8938</v>
       </c>
     </row>
     <row r="3">
@@ -464,6 +470,9 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C3">
+        <v>63.4122</v>
+      </c>
       <c r="D3">
         <v>37.782</v>
       </c>
@@ -505,34 +514,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>55.505</v>
+        <v>49.7955</v>
       </c>
       <c r="D4">
-        <v>40.41966666666666</v>
+        <v>60.23</v>
       </c>
       <c r="E4">
-        <v>68.14966666666666</v>
+        <v>66.1314</v>
       </c>
       <c r="F4">
-        <v>58.09766666666667</v>
+        <v>46.3978</v>
       </c>
       <c r="G4">
-        <v>50.7745</v>
+        <v>45.319</v>
       </c>
       <c r="H4">
-        <v>59.848</v>
+        <v>46.52033333333333</v>
       </c>
       <c r="I4">
-        <v>59.69133333333334</v>
+        <v>41.13433333333333</v>
       </c>
       <c r="J4">
-        <v>64.11033333333333</v>
+        <v>38.83116666666667</v>
       </c>
       <c r="K4">
-        <v>71.22499999999999</v>
+        <v>50.86600000000001</v>
       </c>
       <c r="L4">
-        <v>115.70525</v>
+        <v>52.33416666666667</v>
+      </c>
+      <c r="M4">
+        <v>56.78283333333334</v>
       </c>
     </row>
     <row r="5">
@@ -545,34 +557,37 @@
         </is>
       </c>
       <c r="C5">
-        <v>27.04233333333334</v>
+        <v>10.9155</v>
       </c>
       <c r="D5">
-        <v>50.524</v>
+        <v>13.944</v>
       </c>
       <c r="E5">
-        <v>28.141</v>
+        <v>20.3765</v>
       </c>
       <c r="F5">
-        <v>29.5745</v>
+        <v>27.4252</v>
       </c>
       <c r="G5">
-        <v>27.9095</v>
+        <v>30.86975</v>
       </c>
       <c r="H5">
-        <v>26.603</v>
+        <v>26.7866</v>
       </c>
       <c r="I5">
-        <v>27.1065</v>
+        <v>26.657</v>
       </c>
       <c r="J5">
-        <v>66.164</v>
+        <v>40.3942</v>
+      </c>
+      <c r="K5">
+        <v>40.499</v>
       </c>
       <c r="L5">
-        <v>21.866</v>
+        <v>23.90266666666666</v>
       </c>
       <c r="M5">
-        <v>21.505</v>
+        <v>28.87533333333333</v>
       </c>
     </row>
     <row r="6">
@@ -587,6 +602,9 @@
       <c r="C6">
         <v>34.52275</v>
       </c>
+      <c r="D6">
+        <v>97.29566666666666</v>
+      </c>
       <c r="E6">
         <v>106.1005</v>
       </c>
@@ -598,6 +616,9 @@
       </c>
       <c r="H6">
         <v>120.1488</v>
+      </c>
+      <c r="I6">
+        <v>134.5351666666667</v>
       </c>
       <c r="J6">
         <v>113.4311666666667</v>
@@ -665,34 +686,37 @@
         </is>
       </c>
       <c r="C8">
-        <v>27.6758</v>
+        <v>20.33</v>
+      </c>
+      <c r="D8">
+        <v>25.451</v>
       </c>
       <c r="E8">
-        <v>33.81</v>
+        <v>16.1325</v>
       </c>
       <c r="F8">
-        <v>68.06049999999999</v>
+        <v>29.36366666666666</v>
       </c>
       <c r="G8">
-        <v>55.216</v>
+        <v>37.668</v>
       </c>
       <c r="H8">
-        <v>50.571</v>
+        <v>37.76333333333333</v>
       </c>
       <c r="I8">
-        <v>49.13</v>
+        <v>37.4795</v>
       </c>
       <c r="J8">
-        <v>73.17449999999999</v>
+        <v>48.69240000000001</v>
       </c>
       <c r="K8">
-        <v>67.11199999999999</v>
+        <v>62.59183333333333</v>
       </c>
       <c r="L8">
-        <v>55.01933333333333</v>
+        <v>58.2794</v>
       </c>
       <c r="M8">
-        <v>88.33324999999999</v>
+        <v>56.761</v>
       </c>
     </row>
     <row r="9">
@@ -705,34 +729,37 @@
         </is>
       </c>
       <c r="C9">
-        <v>27.43975</v>
+        <v>13.914</v>
       </c>
       <c r="D9">
-        <v>42.136</v>
+        <v>53.274</v>
+      </c>
+      <c r="E9">
+        <v>96.34033333333333</v>
       </c>
       <c r="F9">
-        <v>78.4264</v>
+        <v>84.06133333333334</v>
       </c>
       <c r="G9">
-        <v>65.39525</v>
+        <v>69.7182</v>
       </c>
       <c r="H9">
-        <v>42.88016666666667</v>
+        <v>73.8635</v>
       </c>
       <c r="I9">
-        <v>67.31399999999999</v>
+        <v>98.97083333333335</v>
       </c>
       <c r="J9">
-        <v>41.66</v>
+        <v>115.5786666666667</v>
       </c>
       <c r="K9">
-        <v>71.40000000000001</v>
+        <v>90.89550000000001</v>
       </c>
       <c r="L9">
-        <v>70.37439999999999</v>
+        <v>76.8646</v>
       </c>
       <c r="M9">
-        <v>72.35725000000001</v>
+        <v>97.8914</v>
       </c>
     </row>
     <row r="10">
@@ -753,8 +780,14 @@
       <c r="E10">
         <v>115.6806666666667</v>
       </c>
+      <c r="G10">
+        <v>139.806</v>
+      </c>
       <c r="H10">
         <v>104.761</v>
+      </c>
+      <c r="I10">
+        <v>123.012</v>
       </c>
       <c r="J10">
         <v>112.1835</v>
@@ -781,6 +814,9 @@
       <c r="C11">
         <v>36.867</v>
       </c>
+      <c r="E11">
+        <v>143.0876666666667</v>
+      </c>
       <c r="F11">
         <v>130.5753333333333</v>
       </c>
@@ -789,6 +825,9 @@
       </c>
       <c r="H11">
         <v>151.4623333333333</v>
+      </c>
+      <c r="I11">
+        <v>126.1868333333333</v>
       </c>
       <c r="J11">
         <v>121.8043333333333</v>
@@ -855,29 +894,38 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C13">
+        <v>29.383</v>
+      </c>
+      <c r="D13">
+        <v>47.73325</v>
+      </c>
       <c r="E13">
-        <v>64.3845</v>
+        <v>55.7916</v>
+      </c>
+      <c r="F13">
+        <v>61.0645</v>
       </c>
       <c r="G13">
-        <v>78.2325</v>
+        <v>37.673</v>
       </c>
       <c r="H13">
-        <v>88.206</v>
+        <v>42.25766666666667</v>
       </c>
       <c r="I13">
-        <v>104.693</v>
+        <v>45.7796</v>
       </c>
       <c r="J13">
-        <v>116.669</v>
+        <v>44.2585</v>
       </c>
       <c r="K13">
-        <v>110.038</v>
+        <v>44.8048</v>
       </c>
       <c r="L13">
-        <v>97.93299999999999</v>
+        <v>42.7734</v>
       </c>
       <c r="M13">
-        <v>62.815</v>
+        <v>44.55183333333333</v>
       </c>
     </row>
     <row r="14">
@@ -933,37 +981,37 @@
         </is>
       </c>
       <c r="C15">
-        <v>7.692</v>
+        <v>17.027</v>
       </c>
       <c r="D15">
-        <v>15.9755</v>
+        <v>78.51140000000001</v>
       </c>
       <c r="E15">
-        <v>15.34066666666667</v>
+        <v>96.7264</v>
       </c>
       <c r="F15">
-        <v>16.57066666666667</v>
+        <v>83.91433333333333</v>
       </c>
       <c r="G15">
-        <v>17.7418</v>
+        <v>79.4136</v>
       </c>
       <c r="H15">
-        <v>18.8942</v>
+        <v>88.95733333333334</v>
       </c>
       <c r="I15">
-        <v>16.8528</v>
+        <v>84.146</v>
       </c>
       <c r="J15">
-        <v>18.4226</v>
+        <v>79.12466666666667</v>
       </c>
       <c r="K15">
-        <v>15.544</v>
+        <v>99.31620000000001</v>
       </c>
       <c r="L15">
-        <v>11.19266666666667</v>
+        <v>73.02799999999999</v>
       </c>
       <c r="M15">
-        <v>17.98833333333333</v>
+        <v>77.42619999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1018,6 +1066,39 @@
           <t>GAG</t>
         </is>
       </c>
+      <c r="C17">
+        <v>44.8365</v>
+      </c>
+      <c r="D17">
+        <v>61.5096</v>
+      </c>
+      <c r="E17">
+        <v>37.7364</v>
+      </c>
+      <c r="F17">
+        <v>68.9455</v>
+      </c>
+      <c r="G17">
+        <v>135.832</v>
+      </c>
+      <c r="H17">
+        <v>95.70180000000001</v>
+      </c>
+      <c r="I17">
+        <v>92.89666666666666</v>
+      </c>
+      <c r="J17">
+        <v>115.6105</v>
+      </c>
+      <c r="K17">
+        <v>122.4655</v>
+      </c>
+      <c r="L17">
+        <v>98.88116666666667</v>
+      </c>
+      <c r="M17">
+        <v>111.6844</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1972,34 +2053,37 @@
         </is>
       </c>
       <c r="C40">
-        <v>9.360749999999999</v>
+        <v>43.01433333333333</v>
       </c>
       <c r="D40">
-        <v>18.1282</v>
+        <v>46.21316666666667</v>
       </c>
       <c r="E40">
-        <v>17.227</v>
+        <v>33.131</v>
       </c>
       <c r="F40">
-        <v>23.38533333333334</v>
+        <v>47.8432</v>
       </c>
       <c r="G40">
-        <v>33.002</v>
+        <v>31.38833333333334</v>
       </c>
       <c r="H40">
-        <v>26.5266</v>
+        <v>23.29316666666667</v>
       </c>
       <c r="I40">
-        <v>26.25966666666666</v>
+        <v>29.25966666666666</v>
       </c>
       <c r="J40">
-        <v>28.81166666666667</v>
+        <v>38.08783333333334</v>
       </c>
       <c r="K40">
-        <v>22.50433333333334</v>
+        <v>43.06266666666667</v>
       </c>
       <c r="L40">
-        <v>61.061</v>
+        <v>38.47466666666667</v>
+      </c>
+      <c r="M40">
+        <v>44.5445</v>
       </c>
     </row>
     <row r="41">
